--- a/Модель_расчета_оборотных_компонентов_NTE.xlsx
+++ b/Модель_расчета_оборотных_компонентов_NTE.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="Сводка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Парк (SAP)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Гарантия (машины)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Потребность (компоненты)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Графики" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Парк (SAP)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Гарантия (машины)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Потребность (компоненты)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2024,12 +2025,12 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2700000"/>
+    <ext cx="5400000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2046,12 +2047,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2700000"/>
+    <ext cx="5400000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -2068,12 +2069,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2700000"/>
+    <ext cx="5400000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -2090,105 +2091,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>51</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7200000" cy="2700000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6840000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6840000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6840000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>25</col>
-      <colOff>0</colOff>
-      <row>56</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="6840000" cy="2520000"/>
+    <ext cx="5400000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -2205,12 +2113,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>25</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2520000"/>
+    <ext cx="5400000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -2227,12 +2135,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>25</col>
+      <col>10</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2520000"/>
+    <ext cx="5400000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -2249,12 +2157,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>25</col>
+      <col>0</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6840000" cy="2520000"/>
+    <ext cx="5400000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -2264,6 +2172,94 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="8" name="Chart 8"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="9" name="Chart 9"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="10" name="Chart 10"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>88</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="11" name="Chart 11"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId11"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -3477,6 +3473,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:S37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ГРАФИКИ: МАШИНЫ НА ГАРАНТИИ И ПОТРЕБНОСТЬ В КОМПОНЕНТАХ ПО ПЛОЩАДКАМ И МОДЕЛЯМ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Раздел 1. Самосвалы на гарантии — по каждой площадке (линии = модели)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Раздел 2. Потребность в оборотных компонентах — по каждой площадке и модели</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A37:S37"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -18046,7 +18083,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21834,11 +21871,10 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30529,6 +30565,5 @@
     <mergeCell ref="U12:W12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Модель_расчета_оборотных_компонентов_NTE.xlsx
+++ b/Модель_расчета_оборотных_компонентов_NTE.xlsx
@@ -22431,7 +22431,7 @@
         <v>2024</v>
       </c>
       <c r="B8" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A8)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A8)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>68</v>
       </c>
       <c r="C8" s="32">
@@ -22439,15 +22439,15 @@
         <v>68</v>
       </c>
       <c r="D8" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))=$A8)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A8)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>0</v>
       </c>
       <c r="E8" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A8)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A8)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>68</v>
       </c>
       <c r="F8" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))&lt;=$A8)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A8)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -22456,7 +22456,7 @@
         <v>2025</v>
       </c>
       <c r="B9" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A9)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A9)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>84</v>
       </c>
       <c r="C9" s="32">
@@ -22464,15 +22464,15 @@
         <v>152</v>
       </c>
       <c r="D9" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))=$A9)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A9)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>0</v>
       </c>
       <c r="E9" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A9)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A9)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>152</v>
       </c>
       <c r="F9" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))&lt;=$A9)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A9)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>0</v>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
         <v>2026</v>
       </c>
       <c r="B10" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A10)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A10)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>85</v>
       </c>
       <c r="C10" s="32">
@@ -22489,15 +22489,15 @@
         <v>237</v>
       </c>
       <c r="D10" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))=$A10)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A10)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>68</v>
       </c>
       <c r="E10" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A10)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A10)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>237</v>
       </c>
       <c r="F10" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))&lt;=$A10)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A10)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>68</v>
       </c>
     </row>
@@ -22506,7 +22506,7 @@
         <v>2027</v>
       </c>
       <c r="B11" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A11)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A11)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>58</v>
       </c>
       <c r="C11" s="32">
@@ -22514,15 +22514,15 @@
         <v>227</v>
       </c>
       <c r="D11" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))=$A11)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A11)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>84</v>
       </c>
       <c r="E11" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A11)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A11)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>295</v>
       </c>
       <c r="F11" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))&lt;=$A11)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A11)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>152</v>
       </c>
     </row>
@@ -22531,7 +22531,7 @@
         <v>2028</v>
       </c>
       <c r="B12" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A12)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A12)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>38</v>
       </c>
       <c r="C12" s="32">
@@ -22539,15 +22539,15 @@
         <v>181</v>
       </c>
       <c r="D12" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))=$A12)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A12)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>85</v>
       </c>
       <c r="E12" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A12)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A12)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>333</v>
       </c>
       <c r="F12" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))&lt;=$A12)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A12)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>237</v>
       </c>
     </row>
@@ -22556,7 +22556,7 @@
         <v>2029</v>
       </c>
       <c r="B13" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A13)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A13)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>3</v>
       </c>
       <c r="C13" s="32">
@@ -22564,15 +22564,15 @@
         <v>99</v>
       </c>
       <c r="D13" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))=$A13)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A13)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>58</v>
       </c>
       <c r="E13" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A13)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A13)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>336</v>
       </c>
       <c r="F13" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))&lt;=$A13)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A13)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>295</v>
       </c>
     </row>
@@ -22581,7 +22581,7 @@
         <v>2030</v>
       </c>
       <c r="B14" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A14)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A14)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>0</v>
       </c>
       <c r="C14" s="32">
@@ -22589,15 +22589,15 @@
         <v>41</v>
       </c>
       <c r="D14" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))=$A14)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A14)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>38</v>
       </c>
       <c r="E14" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A14)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A14)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>336</v>
       </c>
       <c r="F14" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))&lt;=$A14)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A14)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>333</v>
       </c>
     </row>
@@ -22606,7 +22606,7 @@
         <v>2031</v>
       </c>
       <c r="B15" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A15)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A15)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>0</v>
       </c>
       <c r="C15" s="32">
@@ -22614,15 +22614,15 @@
         <v>3</v>
       </c>
       <c r="D15" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))=$A15)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A15)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>3</v>
       </c>
       <c r="E15" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A15)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A15)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>336</v>
       </c>
       <c r="F15" s="32">
-        <f>SUMPRODUCT((YEAR(EDATE('Парк (SAP)'!$H$11:$H$346,$C5))&lt;=$A15)*(IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A15)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>336</v>
       </c>
     </row>
@@ -22637,7 +22637,7 @@
         <v>336</v>
       </c>
       <c r="C16" s="35">
-        <f>SUMPRODUCT((IF($C4="(Все)",1,('Парк (SAP)'!$B$11:$B$346=$C4)))*(IF($G4="(Все)",1,('Парк (SAP)'!$C$11:$C$346=$G4))))</f>
+        <f>SUMPRODUCT(((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>336</v>
       </c>
       <c r="D16" s="35">

--- a/Модель_расчета_оборотных_компонентов_NTE.xlsx
+++ b/Модель_расчета_оборотных_компонентов_NTE.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Графики" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Парк (SAP)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Гарантия (машины)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ОФ - расчёт по годам" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ОФ - расчёт по месяцам" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Потребность (компоненты)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
@@ -21,10 +21,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="ММ.ГГГГ"/>
     <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="166" formatCode="MMM YYYY"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="168" formatCode="mm.yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -264,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -349,6 +351,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -917,6 +922,7 @@
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -927,7 +933,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Машин в эксплуатации, на гарантии, сошло с гарантии — по годам</a:t>
+              <a:t>Машин в эксплуатации, на гарантии, сошло с гарантии — по месяцам</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -941,11 +947,11 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'ОФ - расчёт по годам'!C7</f>
+              <f>'ОФ - расчёт по месяцам'!C7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
                 <a:srgbClr val="2E75B6"/>
               </a:solidFill>
@@ -954,7 +960,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="5"/>
+            <size val="3"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="2E75B6"/>
@@ -969,12 +975,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ОФ - расчёт по годам'!$A$8:$A$15</f>
+              <f>'ОФ - расчёт по месяцам'!$A$8:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ОФ - расчёт по годам'!$C$8:$C$15</f>
+              <f>'ОФ - расчёт по месяцам'!$C$8:$C$103</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -984,11 +990,11 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'ОФ - расчёт по годам'!D7</f>
+              <f>'ОФ - расчёт по месяцам'!D7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
                 <a:srgbClr val="1F4E78"/>
               </a:solidFill>
@@ -997,7 +1003,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="5"/>
+            <size val="3"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1F4E78"/>
@@ -1012,12 +1018,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ОФ - расчёт по годам'!$A$8:$A$15</f>
+              <f>'ОФ - расчёт по месяцам'!$A$8:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ОФ - расчёт по годам'!$D$8:$D$15</f>
+              <f>'ОФ - расчёт по месяцам'!$D$8:$D$103</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1027,11 +1033,11 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'ОФ - расчёт по годам'!E7</f>
+              <f>'ОФ - расчёт по месяцам'!E7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
                 <a:srgbClr val="C55A11"/>
               </a:solidFill>
@@ -1040,7 +1046,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="5"/>
+            <size val="3"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="C55A11"/>
@@ -1055,12 +1061,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ОФ - расчёт по годам'!$A$8:$A$15</f>
+              <f>'ОФ - расчёт по месяцам'!$A$8:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ОФ - расчёт по годам'!$E$8:$E$15</f>
+              <f>'ОФ - расчёт по месяцам'!$E$8:$E$103</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1070,11 +1076,11 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'ОФ - расчёт по годам'!F7</f>
+              <f>'ОФ - расчёт по месяцам'!F7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="18000">
               <a:solidFill>
                 <a:srgbClr val="7030A0"/>
               </a:solidFill>
@@ -1083,7 +1089,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="5"/>
+            <size val="3"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="7030A0"/>
@@ -1098,20 +1104,18 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ОФ - расчёт по годам'!$A$8:$A$15</f>
+              <f>'ОФ - расчёт по месяцам'!$A$8:$A$103</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ОФ - расчёт по годам'!$F$8:$F$15</f>
+              <f>'ОФ - расчёт по месяцам'!$F$8:$F$103</f>
             </numRef>
           </val>
           <smooth val="0"/>
         </ser>
         <dLbls>
-          <numFmt formatCode="0"/>
-          <dLblPos val="t"/>
-          <showVal val="1"/>
+          <showVal val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -1132,14 +1136,16 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Год</a:t>
+                  <a:t>Месяц</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="mm.yyyy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -2697,10 +2703,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="3600000"/>
+    <ext cx="10800000" cy="3960000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -22330,10 +22336,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -22344,14 +22350,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОФ — РАСЧЁТ ПО ГОДАМ (ПО ПЛОЩАДКАМ И МОДЕЛЯМ)</t>
+          <t>ОФ — РАСЧЁТ ПО МЕСЯЦАМ (ПО ПЛОЩАДКАМ И МОДЕЛЯМ)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Отдельный годовой расчёт (аналог отчёта Power BI): ввод в эксплуатацию, парк на гарантии, выход из гарантии — по годам, с фильтром по площадке и марке. Срок гарантии здесь — единый параметр (упрощение для этого расчёта); детальный расчёт с раздельным сроком NTE/TR100 — на листе «Парк (SAP)».</t>
+          <t>Отдельный помесячный расчёт (аналог отчёта Power BI): ввод в эксплуатацию, парк на гарантии, выход из гарантии — по месяцам, с фильтром по площадке и марке. Срок гарантии здесь — единый параметр (упрощение для этого расчёта); детальный расчёт с раздельным сроком NTE/TR100 — на листе «Парк (SAP)».</t>
         </is>
       </c>
     </row>
@@ -22389,10 +22395,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="40" t="inlineStr">
         <is>
-          <t>Год</t>
+          <t>Месяц</t>
         </is>
       </c>
       <c r="B7" s="40" t="inlineStr">
@@ -22427,229 +22433,2429 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="n">
-        <v>2024</v>
+      <c r="A8" s="42" t="n">
+        <v>45292</v>
       </c>
       <c r="B8" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A8)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>68</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A8)*12+MONTH($A8)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
       <c r="C8" s="32">
         <f>E8</f>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D8" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A8)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A8)*12+MONTH($A8)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>0</v>
       </c>
       <c r="E8" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A8)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>68</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A8)*12+MONTH($A8)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
       <c r="F8" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A8)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A8)*12+MONTH($A8)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="n">
-        <v>2025</v>
+      <c r="A9" s="42" t="n">
+        <v>45323</v>
       </c>
       <c r="B9" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A9)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>84</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A9)*12+MONTH($A9)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
       </c>
       <c r="C9" s="32">
         <f>E9-F8</f>
-        <v>152</v>
+        <v>9</v>
       </c>
       <c r="D9" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A9)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A9)*12+MONTH($A9)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>0</v>
       </c>
       <c r="E9" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A9)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>152</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A9)*12+MONTH($A9)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
       </c>
       <c r="F9" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A9)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A9)*12+MONTH($A9)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="n">
-        <v>2026</v>
+      <c r="A10" s="42" t="n">
+        <v>45352</v>
       </c>
       <c r="B10" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A10)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>85</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A10)*12+MONTH($A10)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>10</v>
       </c>
       <c r="C10" s="32">
         <f>E10-F9</f>
-        <v>237</v>
+        <v>19</v>
       </c>
       <c r="D10" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A10)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>68</v>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A10)*12+MONTH($A10)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
       <c r="E10" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A10)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>237</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A10)*12+MONTH($A10)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>19</v>
       </c>
       <c r="F10" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A10)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>68</v>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A10)*12+MONTH($A10)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="n">
-        <v>2027</v>
+      <c r="A11" s="42" t="n">
+        <v>45383</v>
       </c>
       <c r="B11" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A11)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>58</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A11)*12+MONTH($A11)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>10</v>
       </c>
       <c r="C11" s="32">
         <f>E11-F10</f>
-        <v>227</v>
+        <v>29</v>
       </c>
       <c r="D11" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A11)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>84</v>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A11)*12+MONTH($A11)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
       <c r="E11" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A11)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>295</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A11)*12+MONTH($A11)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>29</v>
       </c>
       <c r="F11" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A11)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>152</v>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A11)*12+MONTH($A11)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="n">
-        <v>2028</v>
+      <c r="A12" s="42" t="n">
+        <v>45413</v>
       </c>
       <c r="B12" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A12)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>38</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A12)*12+MONTH($A12)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>11</v>
       </c>
       <c r="C12" s="32">
         <f>E12-F11</f>
-        <v>181</v>
+        <v>40</v>
       </c>
       <c r="D12" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A12)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>85</v>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A12)*12+MONTH($A12)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
       <c r="E12" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A12)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>333</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A12)*12+MONTH($A12)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>40</v>
       </c>
       <c r="F12" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A12)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>237</v>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A12)*12+MONTH($A12)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="n">
-        <v>2029</v>
+      <c r="A13" s="42" t="n">
+        <v>45444</v>
       </c>
       <c r="B13" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A13)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>3</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A13)*12+MONTH($A13)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>5</v>
       </c>
       <c r="C13" s="32">
         <f>E13-F12</f>
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="D13" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A13)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>58</v>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A13)*12+MONTH($A13)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
       <c r="E13" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A13)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>336</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A13)*12+MONTH($A13)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>45</v>
       </c>
       <c r="F13" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A13)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>295</v>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A13)*12+MONTH($A13)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="n">
-        <v>2030</v>
+      <c r="A14" s="42" t="n">
+        <v>45474</v>
       </c>
       <c r="B14" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A14)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>0</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A14)*12+MONTH($A14)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
       </c>
       <c r="C14" s="32">
         <f>E14-F13</f>
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D14" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A14)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>38</v>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A14)*12+MONTH($A14)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
       <c r="E14" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A14)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>336</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A14)*12+MONTH($A14)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>54</v>
       </c>
       <c r="F14" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A14)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>333</v>
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A14)*12+MONTH($A14)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="n">
-        <v>2031</v>
+      <c r="A15" s="42" t="n">
+        <v>45505</v>
       </c>
       <c r="B15" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)=$A15)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
-        <v>0</v>
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A15)*12+MONTH($A15)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>2</v>
       </c>
       <c r="C15" s="32">
         <f>E15-F14</f>
+        <v>56</v>
+      </c>
+      <c r="D15" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A15)*12+MONTH($A15)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A15)*12+MONTH($A15)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>56</v>
+      </c>
+      <c r="F15" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A15)*12+MONTH($A15)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B16" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A16)*12+MONTH($A16)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C16" s="32">
+        <f>E16-F15</f>
+        <v>60</v>
+      </c>
+      <c r="D16" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A16)*12+MONTH($A16)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A16)*12+MONTH($A16)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>60</v>
+      </c>
+      <c r="F16" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A16)*12+MONTH($A16)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="42" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B17" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A17)*12+MONTH($A17)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>2</v>
+      </c>
+      <c r="C17" s="32">
+        <f>E17-F16</f>
+        <v>62</v>
+      </c>
+      <c r="D17" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A17)*12+MONTH($A17)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A17)*12+MONTH($A17)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>62</v>
+      </c>
+      <c r="F17" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A17)*12+MONTH($A17)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="42" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B18" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A18)*12+MONTH($A18)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="32">
+        <f>E18-F17</f>
+        <v>62</v>
+      </c>
+      <c r="D18" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A18)*12+MONTH($A18)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A18)*12+MONTH($A18)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>62</v>
+      </c>
+      <c r="F18" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A18)*12+MONTH($A18)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="42" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B19" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A19)*12+MONTH($A19)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>6</v>
+      </c>
+      <c r="C19" s="32">
+        <f>E19-F18</f>
+        <v>68</v>
+      </c>
+      <c r="D19" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A19)*12+MONTH($A19)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A19)*12+MONTH($A19)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>68</v>
+      </c>
+      <c r="F19" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A19)*12+MONTH($A19)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B20" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A20)*12+MONTH($A20)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>10</v>
+      </c>
+      <c r="C20" s="32">
+        <f>E20-F19</f>
+        <v>78</v>
+      </c>
+      <c r="D20" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A20)*12+MONTH($A20)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A20)*12+MONTH($A20)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>78</v>
+      </c>
+      <c r="F20" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A20)*12+MONTH($A20)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="42" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B21" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A21)*12+MONTH($A21)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
+      </c>
+      <c r="C21" s="32">
+        <f>E21-F20</f>
+        <v>87</v>
+      </c>
+      <c r="D21" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A21)*12+MONTH($A21)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A21)*12+MONTH($A21)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>87</v>
+      </c>
+      <c r="F21" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A21)*12+MONTH($A21)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="42" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B22" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A22)*12+MONTH($A22)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>13</v>
+      </c>
+      <c r="C22" s="32">
+        <f>E22-F21</f>
+        <v>100</v>
+      </c>
+      <c r="D22" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A22)*12+MONTH($A22)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A22)*12+MONTH($A22)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>100</v>
+      </c>
+      <c r="F22" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A22)*12+MONTH($A22)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="42" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B23" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A23)*12+MONTH($A23)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>7</v>
+      </c>
+      <c r="C23" s="32">
+        <f>E23-F22</f>
+        <v>107</v>
+      </c>
+      <c r="D23" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A23)*12+MONTH($A23)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A23)*12+MONTH($A23)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>107</v>
+      </c>
+      <c r="F23" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A23)*12+MONTH($A23)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B24" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A24)*12+MONTH($A24)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C24" s="32">
+        <f>E24-F23</f>
+        <v>111</v>
+      </c>
+      <c r="D24" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A24)*12+MONTH($A24)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A24)*12+MONTH($A24)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>111</v>
+      </c>
+      <c r="F24" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A24)*12+MONTH($A24)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B25" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A25)*12+MONTH($A25)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C25" s="32">
+        <f>E25-F24</f>
+        <v>115</v>
+      </c>
+      <c r="D25" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A25)*12+MONTH($A25)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A25)*12+MONTH($A25)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>115</v>
+      </c>
+      <c r="F25" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A25)*12+MONTH($A25)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="42" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B26" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A26)*12+MONTH($A26)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>7</v>
+      </c>
+      <c r="C26" s="32">
+        <f>E26-F25</f>
+        <v>122</v>
+      </c>
+      <c r="D26" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A26)*12+MONTH($A26)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A26)*12+MONTH($A26)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>122</v>
+      </c>
+      <c r="F26" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A26)*12+MONTH($A26)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="42" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B27" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A27)*12+MONTH($A27)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>5</v>
+      </c>
+      <c r="C27" s="32">
+        <f>E27-F26</f>
+        <v>127</v>
+      </c>
+      <c r="D27" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A27)*12+MONTH($A27)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A27)*12+MONTH($A27)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>127</v>
+      </c>
+      <c r="F27" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A27)*12+MONTH($A27)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B28" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A28)*12+MONTH($A28)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
+      </c>
+      <c r="C28" s="32">
+        <f>E28-F27</f>
+        <v>136</v>
+      </c>
+      <c r="D28" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A28)*12+MONTH($A28)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A28)*12+MONTH($A28)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>136</v>
+      </c>
+      <c r="F28" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A28)*12+MONTH($A28)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="42" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B29" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A29)*12+MONTH($A29)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>8</v>
+      </c>
+      <c r="C29" s="32">
+        <f>E29-F28</f>
+        <v>144</v>
+      </c>
+      <c r="D29" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A29)*12+MONTH($A29)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A29)*12+MONTH($A29)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>144</v>
+      </c>
+      <c r="F29" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A29)*12+MONTH($A29)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B30" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A30)*12+MONTH($A30)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>1</v>
+      </c>
+      <c r="C30" s="32">
+        <f>E30-F29</f>
+        <v>145</v>
+      </c>
+      <c r="D30" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A30)*12+MONTH($A30)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A30)*12+MONTH($A30)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>145</v>
+      </c>
+      <c r="F30" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A30)*12+MONTH($A30)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B31" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A31)*12+MONTH($A31)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>7</v>
+      </c>
+      <c r="C31" s="32">
+        <f>E31-F30</f>
+        <v>152</v>
+      </c>
+      <c r="D31" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A31)*12+MONTH($A31)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A31)*12+MONTH($A31)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>152</v>
+      </c>
+      <c r="F31" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A31)*12+MONTH($A31)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="42" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B32" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A32)*12+MONTH($A32)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>6</v>
+      </c>
+      <c r="C32" s="32">
+        <f>E32-F31</f>
+        <v>158</v>
+      </c>
+      <c r="D32" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A32)*12+MONTH($A32)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A32)*12+MONTH($A32)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>158</v>
+      </c>
+      <c r="F32" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A32)*12+MONTH($A32)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="42" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B33" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A33)*12+MONTH($A33)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>11</v>
+      </c>
+      <c r="C33" s="32">
+        <f>E33-F32</f>
+        <v>169</v>
+      </c>
+      <c r="D33" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A33)*12+MONTH($A33)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
+      </c>
+      <c r="E33" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A33)*12+MONTH($A33)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>169</v>
+      </c>
+      <c r="F33" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A33)*12+MONTH($A33)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="42" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B34" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A34)*12+MONTH($A34)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>13</v>
+      </c>
+      <c r="C34" s="32">
+        <f>E34-F33</f>
+        <v>173</v>
+      </c>
+      <c r="D34" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A34)*12+MONTH($A34)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>10</v>
+      </c>
+      <c r="E34" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A34)*12+MONTH($A34)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>182</v>
+      </c>
+      <c r="F34" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A34)*12+MONTH($A34)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="42" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B35" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A35)*12+MONTH($A35)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
+      </c>
+      <c r="C35" s="32">
+        <f>E35-F34</f>
+        <v>172</v>
+      </c>
+      <c r="D35" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A35)*12+MONTH($A35)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>10</v>
+      </c>
+      <c r="E35" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A35)*12+MONTH($A35)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>191</v>
+      </c>
+      <c r="F35" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A35)*12+MONTH($A35)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B36" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A36)*12+MONTH($A36)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>5</v>
+      </c>
+      <c r="C36" s="32">
+        <f>E36-F35</f>
+        <v>167</v>
+      </c>
+      <c r="D36" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A36)*12+MONTH($A36)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>11</v>
+      </c>
+      <c r="E36" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A36)*12+MONTH($A36)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>196</v>
+      </c>
+      <c r="F36" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A36)*12+MONTH($A36)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="42" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B37" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A37)*12+MONTH($A37)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>6</v>
+      </c>
+      <c r="C37" s="32">
+        <f>E37-F36</f>
+        <v>162</v>
+      </c>
+      <c r="D37" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A37)*12+MONTH($A37)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>5</v>
+      </c>
+      <c r="E37" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A37)*12+MONTH($A37)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>202</v>
+      </c>
+      <c r="F37" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A37)*12+MONTH($A37)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="42" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B38" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A38)*12+MONTH($A38)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>2</v>
+      </c>
+      <c r="C38" s="32">
+        <f>E38-F37</f>
+        <v>159</v>
+      </c>
+      <c r="D38" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A38)*12+MONTH($A38)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
+      </c>
+      <c r="E38" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A38)*12+MONTH($A38)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>204</v>
+      </c>
+      <c r="F38" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A38)*12+MONTH($A38)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="42" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B39" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A39)*12+MONTH($A39)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C39" s="32">
+        <f>E39-F38</f>
+        <v>150</v>
+      </c>
+      <c r="D39" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A39)*12+MONTH($A39)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>2</v>
+      </c>
+      <c r="E39" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A39)*12+MONTH($A39)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>204</v>
+      </c>
+      <c r="F39" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A39)*12+MONTH($A39)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="42" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B40" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A40)*12+MONTH($A40)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>5</v>
+      </c>
+      <c r="C40" s="32">
+        <f>E40-F39</f>
+        <v>153</v>
+      </c>
+      <c r="D40" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A40)*12+MONTH($A40)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E40" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A40)*12+MONTH($A40)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>209</v>
+      </c>
+      <c r="F40" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A40)*12+MONTH($A40)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="42" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B41" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A41)*12+MONTH($A41)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
+      </c>
+      <c r="C41" s="32">
+        <f>E41-F40</f>
+        <v>158</v>
+      </c>
+      <c r="D41" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A41)*12+MONTH($A41)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>2</v>
+      </c>
+      <c r="E41" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A41)*12+MONTH($A41)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>218</v>
+      </c>
+      <c r="F41" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A41)*12+MONTH($A41)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="42" t="n">
+        <v>46327</v>
+      </c>
+      <c r="B42" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A42)*12+MONTH($A42)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>13</v>
+      </c>
+      <c r="C42" s="32">
+        <f>E42-F41</f>
+        <v>169</v>
+      </c>
+      <c r="D42" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A42)*12+MONTH($A42)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A42)*12+MONTH($A42)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>231</v>
+      </c>
+      <c r="F42" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A42)*12+MONTH($A42)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="42" t="n">
+        <v>46357</v>
+      </c>
+      <c r="B43" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A43)*12+MONTH($A43)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>6</v>
+      </c>
+      <c r="C43" s="32">
+        <f>E43-F42</f>
+        <v>175</v>
+      </c>
+      <c r="D43" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A43)*12+MONTH($A43)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>6</v>
+      </c>
+      <c r="E43" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A43)*12+MONTH($A43)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>237</v>
+      </c>
+      <c r="F43" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A43)*12+MONTH($A43)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="42" t="n">
+        <v>46388</v>
+      </c>
+      <c r="B44" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A44)*12+MONTH($A44)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>8</v>
+      </c>
+      <c r="C44" s="32">
+        <f>E44-F43</f>
+        <v>177</v>
+      </c>
+      <c r="D44" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A44)*12+MONTH($A44)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>10</v>
+      </c>
+      <c r="E44" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A44)*12+MONTH($A44)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>245</v>
+      </c>
+      <c r="F44" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A44)*12+MONTH($A44)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="42" t="n">
+        <v>46419</v>
+      </c>
+      <c r="B45" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A45)*12+MONTH($A45)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>7</v>
+      </c>
+      <c r="C45" s="32">
+        <f>E45-F44</f>
+        <v>174</v>
+      </c>
+      <c r="D45" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A45)*12+MONTH($A45)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
+      </c>
+      <c r="E45" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A45)*12+MONTH($A45)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>252</v>
+      </c>
+      <c r="F45" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A45)*12+MONTH($A45)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="n">
+        <v>46447</v>
+      </c>
+      <c r="B46" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A46)*12+MONTH($A46)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C46" s="32">
+        <f>E46-F45</f>
+        <v>165</v>
+      </c>
+      <c r="D46" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A46)*12+MONTH($A46)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>13</v>
+      </c>
+      <c r="E46" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A46)*12+MONTH($A46)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>252</v>
+      </c>
+      <c r="F46" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A46)*12+MONTH($A46)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="42" t="n">
+        <v>46478</v>
+      </c>
+      <c r="B47" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A47)*12+MONTH($A47)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>8</v>
+      </c>
+      <c r="C47" s="32">
+        <f>E47-F46</f>
+        <v>160</v>
+      </c>
+      <c r="D47" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A47)*12+MONTH($A47)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>7</v>
+      </c>
+      <c r="E47" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A47)*12+MONTH($A47)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>260</v>
+      </c>
+      <c r="F47" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A47)*12+MONTH($A47)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="42" t="n">
+        <v>46508</v>
+      </c>
+      <c r="B48" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A48)*12+MONTH($A48)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>7</v>
+      </c>
+      <c r="C48" s="32">
+        <f>E48-F47</f>
+        <v>160</v>
+      </c>
+      <c r="D48" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A48)*12+MONTH($A48)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E48" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A48)*12+MONTH($A48)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>267</v>
+      </c>
+      <c r="F48" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A48)*12+MONTH($A48)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="42" t="n">
+        <v>46539</v>
+      </c>
+      <c r="B49" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A49)*12+MONTH($A49)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C49" s="32">
+        <f>E49-F48</f>
+        <v>160</v>
+      </c>
+      <c r="D49" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A49)*12+MONTH($A49)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E49" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A49)*12+MONTH($A49)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>271</v>
+      </c>
+      <c r="F49" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A49)*12+MONTH($A49)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="42" t="n">
+        <v>46569</v>
+      </c>
+      <c r="B50" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A50)*12+MONTH($A50)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>3</v>
       </c>
-      <c r="D15" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))=$A15)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+      <c r="C50" s="32">
+        <f>E50-F49</f>
+        <v>159</v>
+      </c>
+      <c r="D50" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A50)*12+MONTH($A50)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>7</v>
+      </c>
+      <c r="E50" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A50)*12+MONTH($A50)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>274</v>
+      </c>
+      <c r="F50" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A50)*12+MONTH($A50)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="42" t="n">
+        <v>46600</v>
+      </c>
+      <c r="B51" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A51)*12+MONTH($A51)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>5</v>
+      </c>
+      <c r="C51" s="32">
+        <f>E51-F50</f>
+        <v>157</v>
+      </c>
+      <c r="D51" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A51)*12+MONTH($A51)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>5</v>
+      </c>
+      <c r="E51" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A51)*12+MONTH($A51)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>279</v>
+      </c>
+      <c r="F51" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A51)*12+MONTH($A51)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="42" t="n">
+        <v>46631</v>
+      </c>
+      <c r="B52" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A52)*12+MONTH($A52)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C52" s="32">
+        <f>E52-F51</f>
+        <v>156</v>
+      </c>
+      <c r="D52" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A52)*12+MONTH($A52)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
+      </c>
+      <c r="E52" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A52)*12+MONTH($A52)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>283</v>
+      </c>
+      <c r="F52" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A52)*12+MONTH($A52)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="42" t="n">
+        <v>46661</v>
+      </c>
+      <c r="B53" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A53)*12+MONTH($A53)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C53" s="32">
+        <f>E53-F52</f>
+        <v>151</v>
+      </c>
+      <c r="D53" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A53)*12+MONTH($A53)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>8</v>
+      </c>
+      <c r="E53" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A53)*12+MONTH($A53)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>287</v>
+      </c>
+      <c r="F53" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A53)*12+MONTH($A53)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="42" t="n">
+        <v>46692</v>
+      </c>
+      <c r="B54" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A54)*12+MONTH($A54)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C54" s="32">
+        <f>E54-F53</f>
+        <v>147</v>
+      </c>
+      <c r="D54" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A54)*12+MONTH($A54)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>1</v>
+      </c>
+      <c r="E54" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A54)*12+MONTH($A54)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>291</v>
+      </c>
+      <c r="F54" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A54)*12+MONTH($A54)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="42" t="n">
+        <v>46722</v>
+      </c>
+      <c r="B55" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A55)*12+MONTH($A55)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C55" s="32">
+        <f>E55-F54</f>
+        <v>150</v>
+      </c>
+      <c r="D55" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A55)*12+MONTH($A55)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>7</v>
+      </c>
+      <c r="E55" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A55)*12+MONTH($A55)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>295</v>
+      </c>
+      <c r="F55" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A55)*12+MONTH($A55)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="42" t="n">
+        <v>46753</v>
+      </c>
+      <c r="B56" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A56)*12+MONTH($A56)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>3</v>
       </c>
-      <c r="E15" s="32">
-        <f>SUMPRODUCT((YEAR('Парк (SAP)'!$H$11:$H$346)&lt;=$A15)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+      <c r="C56" s="32">
+        <f>E56-F55</f>
+        <v>146</v>
+      </c>
+      <c r="D56" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A56)*12+MONTH($A56)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>6</v>
+      </c>
+      <c r="E56" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A56)*12+MONTH($A56)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>298</v>
+      </c>
+      <c r="F56" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A56)*12+MONTH($A56)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="42" t="n">
+        <v>46784</v>
+      </c>
+      <c r="B57" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A57)*12+MONTH($A57)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>3</v>
+      </c>
+      <c r="C57" s="32">
+        <f>E57-F56</f>
+        <v>143</v>
+      </c>
+      <c r="D57" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A57)*12+MONTH($A57)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>11</v>
+      </c>
+      <c r="E57" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A57)*12+MONTH($A57)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>301</v>
+      </c>
+      <c r="F57" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A57)*12+MONTH($A57)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="42" t="n">
+        <v>46813</v>
+      </c>
+      <c r="B58" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A58)*12+MONTH($A58)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>3</v>
+      </c>
+      <c r="C58" s="32">
+        <f>E58-F57</f>
+        <v>135</v>
+      </c>
+      <c r="D58" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A58)*12+MONTH($A58)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>13</v>
+      </c>
+      <c r="E58" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A58)*12+MONTH($A58)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>304</v>
+      </c>
+      <c r="F58" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A58)*12+MONTH($A58)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="42" t="n">
+        <v>46844</v>
+      </c>
+      <c r="B59" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A59)*12+MONTH($A59)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C59" s="32">
+        <f>E59-F58</f>
+        <v>126</v>
+      </c>
+      <c r="D59" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A59)*12+MONTH($A59)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
+      </c>
+      <c r="E59" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A59)*12+MONTH($A59)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>308</v>
+      </c>
+      <c r="F59" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A59)*12+MONTH($A59)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="42" t="n">
+        <v>46874</v>
+      </c>
+      <c r="B60" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A60)*12+MONTH($A60)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C60" s="32">
+        <f>E60-F59</f>
+        <v>121</v>
+      </c>
+      <c r="D60" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A60)*12+MONTH($A60)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>5</v>
+      </c>
+      <c r="E60" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A60)*12+MONTH($A60)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>312</v>
+      </c>
+      <c r="F60" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A60)*12+MONTH($A60)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>196</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="42" t="n">
+        <v>46905</v>
+      </c>
+      <c r="B61" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A61)*12+MONTH($A61)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C61" s="32">
+        <f>E61-F60</f>
+        <v>120</v>
+      </c>
+      <c r="D61" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A61)*12+MONTH($A61)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>6</v>
+      </c>
+      <c r="E61" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A61)*12+MONTH($A61)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>316</v>
+      </c>
+      <c r="F61" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A61)*12+MONTH($A61)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>202</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="42" t="n">
+        <v>46935</v>
+      </c>
+      <c r="B62" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A62)*12+MONTH($A62)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>3</v>
+      </c>
+      <c r="C62" s="32">
+        <f>E62-F61</f>
+        <v>117</v>
+      </c>
+      <c r="D62" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A62)*12+MONTH($A62)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>2</v>
+      </c>
+      <c r="E62" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A62)*12+MONTH($A62)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>319</v>
+      </c>
+      <c r="F62" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A62)*12+MONTH($A62)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="42" t="n">
+        <v>46966</v>
+      </c>
+      <c r="B63" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A63)*12+MONTH($A63)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>1</v>
+      </c>
+      <c r="C63" s="32">
+        <f>E63-F62</f>
+        <v>116</v>
+      </c>
+      <c r="D63" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A63)*12+MONTH($A63)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A63)*12+MONTH($A63)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>320</v>
+      </c>
+      <c r="F63" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A63)*12+MONTH($A63)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="42" t="n">
+        <v>46997</v>
+      </c>
+      <c r="B64" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A64)*12+MONTH($A64)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>1</v>
+      </c>
+      <c r="C64" s="32">
+        <f>E64-F63</f>
+        <v>117</v>
+      </c>
+      <c r="D64" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A64)*12+MONTH($A64)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>5</v>
+      </c>
+      <c r="E64" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A64)*12+MONTH($A64)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>321</v>
+      </c>
+      <c r="F64" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A64)*12+MONTH($A64)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="42" t="n">
+        <v>47027</v>
+      </c>
+      <c r="B65" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A65)*12+MONTH($A65)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C65" s="32">
+        <f>E65-F64</f>
+        <v>116</v>
+      </c>
+      <c r="D65" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A65)*12+MONTH($A65)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>9</v>
+      </c>
+      <c r="E65" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A65)*12+MONTH($A65)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>325</v>
+      </c>
+      <c r="F65" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A65)*12+MONTH($A65)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="42" t="n">
+        <v>47058</v>
+      </c>
+      <c r="B66" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A66)*12+MONTH($A66)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C66" s="32">
+        <f>E66-F65</f>
+        <v>111</v>
+      </c>
+      <c r="D66" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A66)*12+MONTH($A66)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>13</v>
+      </c>
+      <c r="E66" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A66)*12+MONTH($A66)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>329</v>
+      </c>
+      <c r="F66" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A66)*12+MONTH($A66)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="42" t="n">
+        <v>47088</v>
+      </c>
+      <c r="B67" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A67)*12+MONTH($A67)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="C67" s="32">
+        <f>E67-F66</f>
+        <v>102</v>
+      </c>
+      <c r="D67" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A67)*12+MONTH($A67)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>6</v>
+      </c>
+      <c r="E67" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A67)*12+MONTH($A67)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>333</v>
+      </c>
+      <c r="F67" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A67)*12+MONTH($A67)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="42" t="n">
+        <v>47119</v>
+      </c>
+      <c r="B68" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A68)*12+MONTH($A68)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>3</v>
+      </c>
+      <c r="C68" s="32">
+        <f>E68-F67</f>
+        <v>99</v>
+      </c>
+      <c r="D68" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A68)*12+MONTH($A68)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>8</v>
+      </c>
+      <c r="E68" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A68)*12+MONTH($A68)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>336</v>
       </c>
-      <c r="F15" s="32">
-        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)+INT((MONTH('Парк (SAP)'!$H$11:$H$346)-1+$C5)/12))&lt;=$A15)*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+      <c r="F68" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A68)*12+MONTH($A68)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="42" t="n">
+        <v>47150</v>
+      </c>
+      <c r="B69" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A69)*12+MONTH($A69)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C69" s="32">
+        <f>E69-F68</f>
+        <v>91</v>
+      </c>
+      <c r="D69" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A69)*12+MONTH($A69)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>7</v>
+      </c>
+      <c r="E69" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A69)*12+MONTH($A69)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>336</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="F69" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A69)*12+MONTH($A69)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="42" t="n">
+        <v>47178</v>
+      </c>
+      <c r="B70" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A70)*12+MONTH($A70)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C70" s="32">
+        <f>E70-F69</f>
+        <v>84</v>
+      </c>
+      <c r="D70" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A70)*12+MONTH($A70)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E70" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A70)*12+MONTH($A70)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F70" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A70)*12+MONTH($A70)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="42" t="n">
+        <v>47209</v>
+      </c>
+      <c r="B71" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A71)*12+MONTH($A71)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C71" s="32">
+        <f>E71-F70</f>
+        <v>84</v>
+      </c>
+      <c r="D71" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A71)*12+MONTH($A71)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>8</v>
+      </c>
+      <c r="E71" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A71)*12+MONTH($A71)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F71" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A71)*12+MONTH($A71)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="42" t="n">
+        <v>47239</v>
+      </c>
+      <c r="B72" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A72)*12+MONTH($A72)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C72" s="32">
+        <f>E72-F71</f>
+        <v>76</v>
+      </c>
+      <c r="D72" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A72)*12+MONTH($A72)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>7</v>
+      </c>
+      <c r="E72" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A72)*12+MONTH($A72)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F72" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A72)*12+MONTH($A72)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>267</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="42" t="n">
+        <v>47270</v>
+      </c>
+      <c r="B73" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A73)*12+MONTH($A73)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C73" s="32">
+        <f>E73-F72</f>
+        <v>69</v>
+      </c>
+      <c r="D73" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A73)*12+MONTH($A73)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E73" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A73)*12+MONTH($A73)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F73" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A73)*12+MONTH($A73)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>271</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="42" t="n">
+        <v>47300</v>
+      </c>
+      <c r="B74" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A74)*12+MONTH($A74)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C74" s="32">
+        <f>E74-F73</f>
+        <v>65</v>
+      </c>
+      <c r="D74" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A74)*12+MONTH($A74)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>3</v>
+      </c>
+      <c r="E74" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A74)*12+MONTH($A74)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F74" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A74)*12+MONTH($A74)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="42" t="n">
+        <v>47331</v>
+      </c>
+      <c r="B75" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A75)*12+MONTH($A75)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C75" s="32">
+        <f>E75-F74</f>
+        <v>62</v>
+      </c>
+      <c r="D75" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A75)*12+MONTH($A75)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>5</v>
+      </c>
+      <c r="E75" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A75)*12+MONTH($A75)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F75" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A75)*12+MONTH($A75)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="42" t="n">
+        <v>47362</v>
+      </c>
+      <c r="B76" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A76)*12+MONTH($A76)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C76" s="32">
+        <f>E76-F75</f>
+        <v>57</v>
+      </c>
+      <c r="D76" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A76)*12+MONTH($A76)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E76" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A76)*12+MONTH($A76)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F76" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A76)*12+MONTH($A76)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="42" t="n">
+        <v>47392</v>
+      </c>
+      <c r="B77" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A77)*12+MONTH($A77)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C77" s="32">
+        <f>E77-F76</f>
+        <v>53</v>
+      </c>
+      <c r="D77" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A77)*12+MONTH($A77)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E77" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A77)*12+MONTH($A77)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F77" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A77)*12+MONTH($A77)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="42" t="n">
+        <v>47423</v>
+      </c>
+      <c r="B78" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A78)*12+MONTH($A78)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C78" s="32">
+        <f>E78-F77</f>
+        <v>49</v>
+      </c>
+      <c r="D78" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A78)*12+MONTH($A78)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E78" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A78)*12+MONTH($A78)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F78" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A78)*12+MONTH($A78)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>291</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="42" t="n">
+        <v>47453</v>
+      </c>
+      <c r="B79" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A79)*12+MONTH($A79)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C79" s="32">
+        <f>E79-F78</f>
+        <v>45</v>
+      </c>
+      <c r="D79" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A79)*12+MONTH($A79)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E79" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A79)*12+MONTH($A79)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F79" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A79)*12+MONTH($A79)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="42" t="n">
+        <v>47484</v>
+      </c>
+      <c r="B80" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A80)*12+MONTH($A80)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C80" s="32">
+        <f>E80-F79</f>
+        <v>41</v>
+      </c>
+      <c r="D80" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A80)*12+MONTH($A80)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>3</v>
+      </c>
+      <c r="E80" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A80)*12+MONTH($A80)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F80" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A80)*12+MONTH($A80)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="42" t="n">
+        <v>47515</v>
+      </c>
+      <c r="B81" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A81)*12+MONTH($A81)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C81" s="32">
+        <f>E81-F80</f>
+        <v>38</v>
+      </c>
+      <c r="D81" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A81)*12+MONTH($A81)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>3</v>
+      </c>
+      <c r="E81" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A81)*12+MONTH($A81)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F81" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A81)*12+MONTH($A81)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="42" t="n">
+        <v>47543</v>
+      </c>
+      <c r="B82" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A82)*12+MONTH($A82)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C82" s="32">
+        <f>E82-F81</f>
+        <v>35</v>
+      </c>
+      <c r="D82" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A82)*12+MONTH($A82)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>3</v>
+      </c>
+      <c r="E82" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A82)*12+MONTH($A82)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F82" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A82)*12+MONTH($A82)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>304</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="42" t="n">
+        <v>47574</v>
+      </c>
+      <c r="B83" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A83)*12+MONTH($A83)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C83" s="32">
+        <f>E83-F82</f>
+        <v>32</v>
+      </c>
+      <c r="D83" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A83)*12+MONTH($A83)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E83" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A83)*12+MONTH($A83)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F83" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A83)*12+MONTH($A83)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="42" t="n">
+        <v>47604</v>
+      </c>
+      <c r="B84" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A84)*12+MONTH($A84)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C84" s="32">
+        <f>E84-F83</f>
+        <v>28</v>
+      </c>
+      <c r="D84" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A84)*12+MONTH($A84)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E84" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A84)*12+MONTH($A84)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F84" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A84)*12+MONTH($A84)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="42" t="n">
+        <v>47635</v>
+      </c>
+      <c r="B85" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A85)*12+MONTH($A85)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C85" s="32">
+        <f>E85-F84</f>
+        <v>24</v>
+      </c>
+      <c r="D85" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A85)*12+MONTH($A85)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E85" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A85)*12+MONTH($A85)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F85" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A85)*12+MONTH($A85)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="42" t="n">
+        <v>47665</v>
+      </c>
+      <c r="B86" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A86)*12+MONTH($A86)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C86" s="32">
+        <f>E86-F85</f>
+        <v>20</v>
+      </c>
+      <c r="D86" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A86)*12+MONTH($A86)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>3</v>
+      </c>
+      <c r="E86" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A86)*12+MONTH($A86)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F86" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A86)*12+MONTH($A86)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="42" t="n">
+        <v>47696</v>
+      </c>
+      <c r="B87" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A87)*12+MONTH($A87)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C87" s="32">
+        <f>E87-F86</f>
+        <v>17</v>
+      </c>
+      <c r="D87" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A87)*12+MONTH($A87)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>1</v>
+      </c>
+      <c r="E87" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A87)*12+MONTH($A87)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F87" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A87)*12+MONTH($A87)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="42" t="n">
+        <v>47727</v>
+      </c>
+      <c r="B88" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A88)*12+MONTH($A88)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C88" s="32">
+        <f>E88-F87</f>
+        <v>16</v>
+      </c>
+      <c r="D88" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A88)*12+MONTH($A88)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>1</v>
+      </c>
+      <c r="E88" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A88)*12+MONTH($A88)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F88" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A88)*12+MONTH($A88)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="42" t="n">
+        <v>47757</v>
+      </c>
+      <c r="B89" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A89)*12+MONTH($A89)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C89" s="32">
+        <f>E89-F88</f>
+        <v>15</v>
+      </c>
+      <c r="D89" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A89)*12+MONTH($A89)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E89" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A89)*12+MONTH($A89)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F89" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A89)*12+MONTH($A89)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="42" t="n">
+        <v>47788</v>
+      </c>
+      <c r="B90" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A90)*12+MONTH($A90)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C90" s="32">
+        <f>E90-F89</f>
+        <v>11</v>
+      </c>
+      <c r="D90" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A90)*12+MONTH($A90)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E90" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A90)*12+MONTH($A90)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F90" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A90)*12+MONTH($A90)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="42" t="n">
+        <v>47818</v>
+      </c>
+      <c r="B91" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A91)*12+MONTH($A91)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C91" s="32">
+        <f>E91-F90</f>
+        <v>7</v>
+      </c>
+      <c r="D91" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A91)*12+MONTH($A91)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>4</v>
+      </c>
+      <c r="E91" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A91)*12+MONTH($A91)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F91" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A91)*12+MONTH($A91)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="42" t="n">
+        <v>47849</v>
+      </c>
+      <c r="B92" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A92)*12+MONTH($A92)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C92" s="32">
+        <f>E92-F91</f>
+        <v>3</v>
+      </c>
+      <c r="D92" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A92)*12+MONTH($A92)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>3</v>
+      </c>
+      <c r="E92" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A92)*12+MONTH($A92)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F92" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A92)*12+MONTH($A92)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="42" t="n">
+        <v>47880</v>
+      </c>
+      <c r="B93" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A93)*12+MONTH($A93)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C93" s="32">
+        <f>E93-F92</f>
+        <v>0</v>
+      </c>
+      <c r="D93" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A93)*12+MONTH($A93)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E93" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A93)*12+MONTH($A93)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F93" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A93)*12+MONTH($A93)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="42" t="n">
+        <v>47908</v>
+      </c>
+      <c r="B94" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A94)*12+MONTH($A94)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C94" s="32">
+        <f>E94-F93</f>
+        <v>0</v>
+      </c>
+      <c r="D94" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A94)*12+MONTH($A94)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A94)*12+MONTH($A94)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F94" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A94)*12+MONTH($A94)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="42" t="n">
+        <v>47939</v>
+      </c>
+      <c r="B95" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A95)*12+MONTH($A95)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C95" s="32">
+        <f>E95-F94</f>
+        <v>0</v>
+      </c>
+      <c r="D95" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A95)*12+MONTH($A95)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E95" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A95)*12+MONTH($A95)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F95" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A95)*12+MONTH($A95)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="42" t="n">
+        <v>47969</v>
+      </c>
+      <c r="B96" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A96)*12+MONTH($A96)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C96" s="32">
+        <f>E96-F95</f>
+        <v>0</v>
+      </c>
+      <c r="D96" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A96)*12+MONTH($A96)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E96" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A96)*12+MONTH($A96)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F96" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A96)*12+MONTH($A96)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="42" t="n">
+        <v>48000</v>
+      </c>
+      <c r="B97" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A97)*12+MONTH($A97)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C97" s="32">
+        <f>E97-F96</f>
+        <v>0</v>
+      </c>
+      <c r="D97" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A97)*12+MONTH($A97)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E97" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A97)*12+MONTH($A97)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F97" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A97)*12+MONTH($A97)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="42" t="n">
+        <v>48030</v>
+      </c>
+      <c r="B98" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A98)*12+MONTH($A98)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C98" s="32">
+        <f>E98-F97</f>
+        <v>0</v>
+      </c>
+      <c r="D98" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A98)*12+MONTH($A98)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E98" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A98)*12+MONTH($A98)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F98" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A98)*12+MONTH($A98)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="42" t="n">
+        <v>48061</v>
+      </c>
+      <c r="B99" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A99)*12+MONTH($A99)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C99" s="32">
+        <f>E99-F98</f>
+        <v>0</v>
+      </c>
+      <c r="D99" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A99)*12+MONTH($A99)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E99" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A99)*12+MONTH($A99)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F99" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A99)*12+MONTH($A99)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="42" t="n">
+        <v>48092</v>
+      </c>
+      <c r="B100" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A100)*12+MONTH($A100)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C100" s="32">
+        <f>E100-F99</f>
+        <v>0</v>
+      </c>
+      <c r="D100" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A100)*12+MONTH($A100)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E100" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A100)*12+MONTH($A100)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F100" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A100)*12+MONTH($A100)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="42" t="n">
+        <v>48122</v>
+      </c>
+      <c r="B101" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A101)*12+MONTH($A101)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C101" s="32">
+        <f>E101-F100</f>
+        <v>0</v>
+      </c>
+      <c r="D101" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A101)*12+MONTH($A101)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E101" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A101)*12+MONTH($A101)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F101" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A101)*12+MONTH($A101)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="42" t="n">
+        <v>48153</v>
+      </c>
+      <c r="B102" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A102)*12+MONTH($A102)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C102" s="32">
+        <f>E102-F101</f>
+        <v>0</v>
+      </c>
+      <c r="D102" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A102)*12+MONTH($A102)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E102" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A102)*12+MONTH($A102)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F102" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A102)*12+MONTH($A102)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="42" t="n">
+        <v>48183</v>
+      </c>
+      <c r="B103" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)=(YEAR($A103)*12+MONTH($A103)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C103" s="32">
+        <f>E103-F102</f>
+        <v>0</v>
+      </c>
+      <c r="D103" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)=(YEAR($A103)*12+MONTH($A103)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>0</v>
+      </c>
+      <c r="E103" s="32">
+        <f>SUMPRODUCT(((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)&lt;=(YEAR($A103)*12+MONTH($A103)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+      <c r="F103" s="32">
+        <f>SUMPRODUCT((((YEAR('Парк (SAP)'!$H$11:$H$346)*12+MONTH('Парк (SAP)'!$H$11:$H$346)-1)+$C5)&lt;=(YEAR($A103)*12+MONTH($A103)-1))*((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="35" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
-      <c r="B16" s="35">
-        <f>SUM(B8:B15)</f>
+      <c r="B104" s="35">
+        <f>SUM(B8:B103)</f>
         <v>336</v>
       </c>
-      <c r="C16" s="35">
+      <c r="C104" s="35">
         <f>SUMPRODUCT(((($C4="(Все)")+('Парк (SAP)'!$B$11:$B$346=$C4)&gt;0))*((($G4="(Все)")+('Парк (SAP)'!$C$11:$C$346=$G4)&gt;0)))</f>
         <v>336</v>
       </c>
-      <c r="D16" s="35">
-        <f>SUM(D8:D15)</f>
+      <c r="D104" s="35">
+        <f>SUM(D8:D103)</f>
         <v>336</v>
       </c>
-      <c r="E16" s="35">
-        <f>E15</f>
+      <c r="E104" s="35">
+        <f>E103</f>
         <v>336</v>
       </c>
-      <c r="F16" s="35">
-        <f>F15</f>
+      <c r="F104" s="35">
+        <f>F103</f>
         <v>336</v>
       </c>
     </row>

--- a/Модель_расчета_оборотных_компонентов_NTE.xlsx
+++ b/Модель_расчета_оборотных_компонентов_NTE.xlsx
@@ -21,12 +21,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="ММ.ГГГГ"/>
     <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
     <numFmt numFmtId="166" formatCode="MMM YYYY"/>
-    <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="168" formatCode="mm.yyyy"/>
+    <numFmt numFmtId="167" formatCode="mm.yyyy"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -266,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -351,7 +350,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -922,7 +924,6 @@
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
   <chart>
     <title>
       <tx>
@@ -1115,7 +1116,9 @@
           <smooth val="0"/>
         </ser>
         <dLbls>
-          <showVal val="0"/>
+          <numFmt formatCode="0"/>
+          <dLblPos val="t"/>
+          <showVal val="1"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -1127,25 +1130,8 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Месяц</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="mm.yyyy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
-        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -22433,7 +22419,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="42" t="n">
+      <c r="A8" s="43" t="n">
         <v>45292</v>
       </c>
       <c r="B8" s="32">
@@ -22458,7 +22444,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="42" t="n">
+      <c r="A9" s="43" t="n">
         <v>45323</v>
       </c>
       <c r="B9" s="32">
@@ -22483,7 +22469,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="42" t="n">
+      <c r="A10" s="43" t="n">
         <v>45352</v>
       </c>
       <c r="B10" s="32">
@@ -22508,7 +22494,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="42" t="n">
+      <c r="A11" s="43" t="n">
         <v>45383</v>
       </c>
       <c r="B11" s="32">
@@ -22533,7 +22519,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="42" t="n">
+      <c r="A12" s="43" t="n">
         <v>45413</v>
       </c>
       <c r="B12" s="32">
@@ -22558,7 +22544,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="42" t="n">
+      <c r="A13" s="43" t="n">
         <v>45444</v>
       </c>
       <c r="B13" s="32">
@@ -22583,7 +22569,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="42" t="n">
+      <c r="A14" s="43" t="n">
         <v>45474</v>
       </c>
       <c r="B14" s="32">
@@ -22608,7 +22594,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="42" t="n">
+      <c r="A15" s="43" t="n">
         <v>45505</v>
       </c>
       <c r="B15" s="32">
@@ -22633,7 +22619,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="42" t="n">
+      <c r="A16" s="43" t="n">
         <v>45536</v>
       </c>
       <c r="B16" s="32">
@@ -22658,7 +22644,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="42" t="n">
+      <c r="A17" s="43" t="n">
         <v>45566</v>
       </c>
       <c r="B17" s="32">
@@ -22683,7 +22669,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="42" t="n">
+      <c r="A18" s="43" t="n">
         <v>45597</v>
       </c>
       <c r="B18" s="32">
@@ -22708,7 +22694,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="42" t="n">
+      <c r="A19" s="43" t="n">
         <v>45627</v>
       </c>
       <c r="B19" s="32">
@@ -22733,7 +22719,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="42" t="n">
+      <c r="A20" s="43" t="n">
         <v>45658</v>
       </c>
       <c r="B20" s="32">
@@ -22758,7 +22744,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="42" t="n">
+      <c r="A21" s="43" t="n">
         <v>45689</v>
       </c>
       <c r="B21" s="32">
@@ -22783,7 +22769,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="42" t="n">
+      <c r="A22" s="43" t="n">
         <v>45717</v>
       </c>
       <c r="B22" s="32">
@@ -22808,7 +22794,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="42" t="n">
+      <c r="A23" s="43" t="n">
         <v>45748</v>
       </c>
       <c r="B23" s="32">
@@ -22833,7 +22819,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="42" t="n">
+      <c r="A24" s="43" t="n">
         <v>45778</v>
       </c>
       <c r="B24" s="32">
@@ -22858,7 +22844,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="42" t="n">
+      <c r="A25" s="43" t="n">
         <v>45809</v>
       </c>
       <c r="B25" s="32">
@@ -22883,7 +22869,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="42" t="n">
+      <c r="A26" s="43" t="n">
         <v>45839</v>
       </c>
       <c r="B26" s="32">
@@ -22908,7 +22894,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="42" t="n">
+      <c r="A27" s="43" t="n">
         <v>45870</v>
       </c>
       <c r="B27" s="32">
@@ -22933,7 +22919,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="42" t="n">
+      <c r="A28" s="43" t="n">
         <v>45901</v>
       </c>
       <c r="B28" s="32">
@@ -22958,7 +22944,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="42" t="n">
+      <c r="A29" s="43" t="n">
         <v>45931</v>
       </c>
       <c r="B29" s="32">
@@ -22983,7 +22969,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="42" t="n">
+      <c r="A30" s="43" t="n">
         <v>45962</v>
       </c>
       <c r="B30" s="32">
@@ -23008,7 +22994,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="42" t="n">
+      <c r="A31" s="43" t="n">
         <v>45992</v>
       </c>
       <c r="B31" s="32">
@@ -23033,7 +23019,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="42" t="n">
+      <c r="A32" s="43" t="n">
         <v>46023</v>
       </c>
       <c r="B32" s="32">
@@ -23058,7 +23044,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="42" t="n">
+      <c r="A33" s="43" t="n">
         <v>46054</v>
       </c>
       <c r="B33" s="32">
@@ -23083,7 +23069,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="42" t="n">
+      <c r="A34" s="43" t="n">
         <v>46082</v>
       </c>
       <c r="B34" s="32">
@@ -23108,7 +23094,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="42" t="n">
+      <c r="A35" s="43" t="n">
         <v>46113</v>
       </c>
       <c r="B35" s="32">
@@ -23133,7 +23119,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="42" t="n">
+      <c r="A36" s="43" t="n">
         <v>46143</v>
       </c>
       <c r="B36" s="32">
@@ -23158,7 +23144,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="42" t="n">
+      <c r="A37" s="43" t="n">
         <v>46174</v>
       </c>
       <c r="B37" s="32">
@@ -23183,7 +23169,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="42" t="n">
+      <c r="A38" s="43" t="n">
         <v>46204</v>
       </c>
       <c r="B38" s="32">
@@ -23208,7 +23194,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="42" t="n">
+      <c r="A39" s="43" t="n">
         <v>46235</v>
       </c>
       <c r="B39" s="32">
@@ -23233,7 +23219,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="42" t="n">
+      <c r="A40" s="43" t="n">
         <v>46266</v>
       </c>
       <c r="B40" s="32">
@@ -23258,7 +23244,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="42" t="n">
+      <c r="A41" s="43" t="n">
         <v>46296</v>
       </c>
       <c r="B41" s="32">
@@ -23283,7 +23269,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="42" t="n">
+      <c r="A42" s="43" t="n">
         <v>46327</v>
       </c>
       <c r="B42" s="32">
@@ -23308,7 +23294,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="42" t="n">
+      <c r="A43" s="43" t="n">
         <v>46357</v>
       </c>
       <c r="B43" s="32">
@@ -23333,7 +23319,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="42" t="n">
+      <c r="A44" s="43" t="n">
         <v>46388</v>
       </c>
       <c r="B44" s="32">
@@ -23358,7 +23344,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="42" t="n">
+      <c r="A45" s="43" t="n">
         <v>46419</v>
       </c>
       <c r="B45" s="32">
@@ -23383,7 +23369,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="42" t="n">
+      <c r="A46" s="43" t="n">
         <v>46447</v>
       </c>
       <c r="B46" s="32">
@@ -23408,7 +23394,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="42" t="n">
+      <c r="A47" s="43" t="n">
         <v>46478</v>
       </c>
       <c r="B47" s="32">
@@ -23433,7 +23419,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="42" t="n">
+      <c r="A48" s="43" t="n">
         <v>46508</v>
       </c>
       <c r="B48" s="32">
@@ -23458,7 +23444,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="42" t="n">
+      <c r="A49" s="43" t="n">
         <v>46539</v>
       </c>
       <c r="B49" s="32">
@@ -23483,7 +23469,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="42" t="n">
+      <c r="A50" s="43" t="n">
         <v>46569</v>
       </c>
       <c r="B50" s="32">
@@ -23508,7 +23494,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="42" t="n">
+      <c r="A51" s="43" t="n">
         <v>46600</v>
       </c>
       <c r="B51" s="32">
@@ -23533,7 +23519,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="42" t="n">
+      <c r="A52" s="43" t="n">
         <v>46631</v>
       </c>
       <c r="B52" s="32">
@@ -23558,7 +23544,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="42" t="n">
+      <c r="A53" s="43" t="n">
         <v>46661</v>
       </c>
       <c r="B53" s="32">
@@ -23583,7 +23569,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="42" t="n">
+      <c r="A54" s="43" t="n">
         <v>46692</v>
       </c>
       <c r="B54" s="32">
@@ -23608,7 +23594,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="42" t="n">
+      <c r="A55" s="43" t="n">
         <v>46722</v>
       </c>
       <c r="B55" s="32">
@@ -23633,7 +23619,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="42" t="n">
+      <c r="A56" s="43" t="n">
         <v>46753</v>
       </c>
       <c r="B56" s="32">
@@ -23658,7 +23644,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="42" t="n">
+      <c r="A57" s="43" t="n">
         <v>46784</v>
       </c>
       <c r="B57" s="32">
@@ -23683,7 +23669,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="42" t="n">
+      <c r="A58" s="43" t="n">
         <v>46813</v>
       </c>
       <c r="B58" s="32">
@@ -23708,7 +23694,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="42" t="n">
+      <c r="A59" s="43" t="n">
         <v>46844</v>
       </c>
       <c r="B59" s="32">
@@ -23733,7 +23719,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="42" t="n">
+      <c r="A60" s="43" t="n">
         <v>46874</v>
       </c>
       <c r="B60" s="32">
@@ -23758,7 +23744,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="42" t="n">
+      <c r="A61" s="43" t="n">
         <v>46905</v>
       </c>
       <c r="B61" s="32">
@@ -23783,7 +23769,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="42" t="n">
+      <c r="A62" s="43" t="n">
         <v>46935</v>
       </c>
       <c r="B62" s="32">
@@ -23808,7 +23794,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="42" t="n">
+      <c r="A63" s="43" t="n">
         <v>46966</v>
       </c>
       <c r="B63" s="32">
@@ -23833,7 +23819,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="42" t="n">
+      <c r="A64" s="43" t="n">
         <v>46997</v>
       </c>
       <c r="B64" s="32">
@@ -23858,7 +23844,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="42" t="n">
+      <c r="A65" s="43" t="n">
         <v>47027</v>
       </c>
       <c r="B65" s="32">
@@ -23883,7 +23869,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="42" t="n">
+      <c r="A66" s="43" t="n">
         <v>47058</v>
       </c>
       <c r="B66" s="32">
@@ -23908,7 +23894,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="42" t="n">
+      <c r="A67" s="43" t="n">
         <v>47088</v>
       </c>
       <c r="B67" s="32">
@@ -23933,7 +23919,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="42" t="n">
+      <c r="A68" s="43" t="n">
         <v>47119</v>
       </c>
       <c r="B68" s="32">
@@ -23958,7 +23944,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="42" t="n">
+      <c r="A69" s="43" t="n">
         <v>47150</v>
       </c>
       <c r="B69" s="32">
@@ -23983,7 +23969,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="42" t="n">
+      <c r="A70" s="43" t="n">
         <v>47178</v>
       </c>
       <c r="B70" s="32">
@@ -24008,7 +23994,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="42" t="n">
+      <c r="A71" s="43" t="n">
         <v>47209</v>
       </c>
       <c r="B71" s="32">
@@ -24033,7 +24019,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="42" t="n">
+      <c r="A72" s="43" t="n">
         <v>47239</v>
       </c>
       <c r="B72" s="32">
@@ -24058,7 +24044,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="42" t="n">
+      <c r="A73" s="43" t="n">
         <v>47270</v>
       </c>
       <c r="B73" s="32">
@@ -24083,7 +24069,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="42" t="n">
+      <c r="A74" s="43" t="n">
         <v>47300</v>
       </c>
       <c r="B74" s="32">
@@ -24108,7 +24094,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="42" t="n">
+      <c r="A75" s="43" t="n">
         <v>47331</v>
       </c>
       <c r="B75" s="32">
@@ -24133,7 +24119,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="42" t="n">
+      <c r="A76" s="43" t="n">
         <v>47362</v>
       </c>
       <c r="B76" s="32">
@@ -24158,7 +24144,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="42" t="n">
+      <c r="A77" s="43" t="n">
         <v>47392</v>
       </c>
       <c r="B77" s="32">
@@ -24183,7 +24169,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="42" t="n">
+      <c r="A78" s="43" t="n">
         <v>47423</v>
       </c>
       <c r="B78" s="32">
@@ -24208,7 +24194,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="42" t="n">
+      <c r="A79" s="43" t="n">
         <v>47453</v>
       </c>
       <c r="B79" s="32">
@@ -24233,7 +24219,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="42" t="n">
+      <c r="A80" s="43" t="n">
         <v>47484</v>
       </c>
       <c r="B80" s="32">
@@ -24258,7 +24244,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="42" t="n">
+      <c r="A81" s="43" t="n">
         <v>47515</v>
       </c>
       <c r="B81" s="32">
@@ -24283,7 +24269,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="42" t="n">
+      <c r="A82" s="43" t="n">
         <v>47543</v>
       </c>
       <c r="B82" s="32">
@@ -24308,7 +24294,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="42" t="n">
+      <c r="A83" s="43" t="n">
         <v>47574</v>
       </c>
       <c r="B83" s="32">
@@ -24333,7 +24319,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="42" t="n">
+      <c r="A84" s="43" t="n">
         <v>47604</v>
       </c>
       <c r="B84" s="32">
@@ -24358,7 +24344,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="42" t="n">
+      <c r="A85" s="43" t="n">
         <v>47635</v>
       </c>
       <c r="B85" s="32">
@@ -24383,7 +24369,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="42" t="n">
+      <c r="A86" s="43" t="n">
         <v>47665</v>
       </c>
       <c r="B86" s="32">
@@ -24408,7 +24394,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="42" t="n">
+      <c r="A87" s="43" t="n">
         <v>47696</v>
       </c>
       <c r="B87" s="32">
@@ -24433,7 +24419,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="42" t="n">
+      <c r="A88" s="43" t="n">
         <v>47727</v>
       </c>
       <c r="B88" s="32">
@@ -24458,7 +24444,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="42" t="n">
+      <c r="A89" s="43" t="n">
         <v>47757</v>
       </c>
       <c r="B89" s="32">
@@ -24483,7 +24469,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="42" t="n">
+      <c r="A90" s="43" t="n">
         <v>47788</v>
       </c>
       <c r="B90" s="32">
@@ -24508,7 +24494,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="42" t="n">
+      <c r="A91" s="43" t="n">
         <v>47818</v>
       </c>
       <c r="B91" s="32">
@@ -24533,7 +24519,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="42" t="n">
+      <c r="A92" s="43" t="n">
         <v>47849</v>
       </c>
       <c r="B92" s="32">
@@ -24558,7 +24544,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="42" t="n">
+      <c r="A93" s="43" t="n">
         <v>47880</v>
       </c>
       <c r="B93" s="32">
@@ -24583,7 +24569,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="42" t="n">
+      <c r="A94" s="43" t="n">
         <v>47908</v>
       </c>
       <c r="B94" s="32">
@@ -24608,7 +24594,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="42" t="n">
+      <c r="A95" s="43" t="n">
         <v>47939</v>
       </c>
       <c r="B95" s="32">
@@ -24633,7 +24619,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="42" t="n">
+      <c r="A96" s="43" t="n">
         <v>47969</v>
       </c>
       <c r="B96" s="32">
@@ -24658,7 +24644,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="42" t="n">
+      <c r="A97" s="43" t="n">
         <v>48000</v>
       </c>
       <c r="B97" s="32">
@@ -24683,7 +24669,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="42" t="n">
+      <c r="A98" s="43" t="n">
         <v>48030</v>
       </c>
       <c r="B98" s="32">
@@ -24708,7 +24694,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="42" t="n">
+      <c r="A99" s="43" t="n">
         <v>48061</v>
       </c>
       <c r="B99" s="32">
@@ -24733,7 +24719,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="42" t="n">
+      <c r="A100" s="43" t="n">
         <v>48092</v>
       </c>
       <c r="B100" s="32">
@@ -24758,7 +24744,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="42" t="n">
+      <c r="A101" s="43" t="n">
         <v>48122</v>
       </c>
       <c r="B101" s="32">
@@ -24783,7 +24769,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="42" t="n">
+      <c r="A102" s="43" t="n">
         <v>48153</v>
       </c>
       <c r="B102" s="32">
@@ -24808,7 +24794,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="42" t="n">
+      <c r="A103" s="43" t="n">
         <v>48183</v>
       </c>
       <c r="B103" s="32">
